--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegist.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegist.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="15210" windowHeight="3480"/>
+    <workbookView xWindow="0" yWindow="2712" windowWidth="15216" windowHeight="3480"/>
   </bookViews>
   <sheets>
     <sheet name="投资者身份信息登记" sheetId="1" r:id="rId1"/>
@@ -22,12 +27,11 @@
     <definedName name="银行">#REF!</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
   <si>
     <t>该投资者是否属于本行</t>
   </si>
@@ -1156,93 +1160,97 @@
   </si>
   <si>
     <t>投资者身份信息登记-导入模板填写说明</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">
 1.新增投资者身份信息登记导入模板
 </t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>3.必填要素前标“**”，选择性必填要素前标“*”，选填要素前无特殊标记；</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>2.必填要素请参照《数据元规范》。</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>**登记银行代码</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>**数据类型</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>**识别标识</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*原识别标识</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*投资者境内外标识</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*投资者类别</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*个人证件类别</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*机构证件类别</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*其他证件名称</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*证件号码</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*投资者名称</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*性别</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*手机号码</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*固定电话</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>*电子邮箱</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>投资者所属国家或地区</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>33 分支机构替代号码</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>34 SPV登记编码</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1252,7 +1260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1317,15 +1325,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1452,69 +1451,66 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1529,19 +1525,14 @@
     <xf numFmtId="49" fontId="8" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="3"/>
-    <cellStyle name="常规 2 2" xfId="2"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="常规 2" xfId="2"/>
+    <cellStyle name="常规 2 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1819,21 +1810,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W4"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21" style="21" customWidth="1"/>
-    <col min="2" max="2" width="23.25" style="21" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="21" customWidth="1"/>
     <col min="3" max="5" width="21" style="21" customWidth="1"/>
-    <col min="6" max="6" width="27.25" style="21" customWidth="1"/>
+    <col min="6" max="6" width="27.21875" style="21" customWidth="1"/>
     <col min="7" max="7" width="21" style="22" customWidth="1"/>
     <col min="8" max="11" width="21" style="21" customWidth="1"/>
-    <col min="12" max="12" width="28.125" style="21" customWidth="1"/>
+    <col min="12" max="12" width="28.109375" style="21" customWidth="1"/>
     <col min="13" max="14" width="21" style="21" customWidth="1"/>
     <col min="15" max="15" width="31" style="21" customWidth="1"/>
-    <col min="16" max="16" width="26.875" style="21" customWidth="1"/>
+    <col min="16" max="16" width="26.88671875" style="21" customWidth="1"/>
     <col min="17" max="23" width="21" style="21" customWidth="1"/>
-    <col min="24" max="16384" width="8.875" style="23"/>
+    <col min="24" max="16384" width="8.88671875" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="13.5" customHeight="1">
@@ -1908,34 +1899,12 @@
       </c>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="22"/>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="J4" s="22"/>
+      <c r="A2" s="21" t="s">
+        <v>364</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
       <formula1>"00 居民身份证,01 临时居民身份证,02 户口簿,10 军官证,11 警官证,12 文职干部证,13 士兵证,14 军事院校学员证,15 离休干部荣誉证,16 军官退休证,17 文职干部退休证,20 中华人民共和国护照,21 外国护照,22 港澳往来内地通行证,23 台湾往来内地通行证,24 外国人永久居留证,99 其他"</formula1>
@@ -1976,9 +1945,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A340"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="82.625" customWidth="1"/>
+    <col min="1" max="1" width="82.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="48" customHeight="1">
@@ -2001,35 +1970,35 @@
         <v>344</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="14.25">
+    <row r="5" spans="1:1" ht="15.6">
       <c r="A5" s="8"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" ht="14.4">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="14.25">
+    <row r="7" spans="1:1" ht="15.6">
       <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" ht="14.4">
       <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" ht="14.4">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" ht="14.4">
       <c r="A10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" ht="14.4">
       <c r="A11" s="11" t="s">
         <v>16</v>
       </c>
@@ -2039,147 +2008,147 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" ht="14.4">
       <c r="A13" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" ht="14.4">
       <c r="A14" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" ht="14.4">
       <c r="A15" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" ht="14.4">
       <c r="A16" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" ht="14.4">
       <c r="A17" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" ht="14.4">
       <c r="A18" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" ht="14.4">
       <c r="A19" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" ht="14.4">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" ht="14.4">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" ht="14.4">
       <c r="A22" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" ht="14.4">
       <c r="A23" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" ht="14.4">
       <c r="A24" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" ht="14.4">
       <c r="A25" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" ht="14.4">
       <c r="A26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" ht="14.4">
       <c r="A27" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" ht="14.4">
       <c r="A28" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" ht="14.4">
       <c r="A29" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" ht="14.4">
       <c r="A30" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" ht="14.4">
       <c r="A31" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" ht="14.4">
       <c r="A32" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" ht="14.4">
       <c r="A33" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" ht="14.4">
       <c r="A34" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" ht="14.4">
       <c r="A35" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" ht="14.4">
       <c r="A36" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" ht="14.4">
       <c r="A37" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" ht="14.4">
       <c r="A38" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" ht="14.4">
       <c r="A39" s="11" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" ht="14.4">
       <c r="A40" s="11" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" ht="14.4">
       <c r="A41" s="15" t="s">
         <v>44</v>
       </c>
@@ -2187,152 +2156,152 @@
     <row r="42" spans="1:1">
       <c r="A42" s="16"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" ht="14.4">
       <c r="A43" s="17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" ht="14.4">
       <c r="A44" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" ht="14.4">
       <c r="A45" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" ht="14.4">
       <c r="A46" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" ht="14.4">
       <c r="A47" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" ht="14.4">
       <c r="A48" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" ht="14.4">
       <c r="A49" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" ht="14.4">
       <c r="A50" s="11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" ht="14.4">
       <c r="A51" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" ht="14.4">
       <c r="A52" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" ht="14.4">
       <c r="A53" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" ht="14.4">
       <c r="A54" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" ht="14.4">
       <c r="A55" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" ht="14.4">
       <c r="A56" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" ht="14.4">
       <c r="A57" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" ht="14.4">
       <c r="A58" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" ht="14.4">
       <c r="A59" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" ht="14.4">
       <c r="A60" s="11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" ht="14.4">
       <c r="A61" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" ht="14.4">
       <c r="A62" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" ht="14.4">
       <c r="A63" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" ht="14.4">
       <c r="A64" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" ht="14.4">
       <c r="A65" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" ht="14.4">
       <c r="A66" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" ht="14.4">
       <c r="A67" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" ht="14.4">
       <c r="A68" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" ht="14.4">
       <c r="A69" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" ht="14.4">
       <c r="A70" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" ht="14.4">
       <c r="A71" s="15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" ht="14.4">
       <c r="A73" s="17" t="s">
         <v>73</v>
       </c>
@@ -2467,7 +2436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" ht="14.4">
       <c r="A101" s="17" t="s">
         <v>99</v>
       </c>
@@ -3527,148 +3496,148 @@
         <v>310</v>
       </c>
     </row>
-    <row r="313" spans="1:1" ht="13.9">
+    <row r="313" spans="1:1">
       <c r="A313" s="19" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="314" spans="1:1" ht="13.9">
+    <row r="314" spans="1:1">
       <c r="A314" s="19" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="315" spans="1:1" ht="13.9">
+    <row r="315" spans="1:1">
       <c r="A315" s="19" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="316" spans="1:1" ht="13.9">
+    <row r="316" spans="1:1">
       <c r="A316" s="19" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="317" spans="1:1" ht="13.9">
+    <row r="317" spans="1:1">
       <c r="A317" s="19" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="318" spans="1:1" ht="13.9">
+    <row r="318" spans="1:1">
       <c r="A318" s="19" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="319" spans="1:1" ht="13.9">
+    <row r="319" spans="1:1">
       <c r="A319" s="19" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="320" spans="1:1" ht="13.9">
+    <row r="320" spans="1:1">
       <c r="A320" s="19" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="321" spans="1:1" ht="13.9">
+    <row r="321" spans="1:1">
       <c r="A321" s="19" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="322" spans="1:1" ht="13.9">
+    <row r="322" spans="1:1">
       <c r="A322" s="19" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="323" spans="1:1" ht="13.9">
+    <row r="323" spans="1:1">
       <c r="A323" s="19" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="324" spans="1:1" ht="13.9">
+    <row r="324" spans="1:1">
       <c r="A324" s="19" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="325" spans="1:1" ht="13.9">
+    <row r="325" spans="1:1">
       <c r="A325" s="19" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="326" spans="1:1" ht="13.9">
+    <row r="326" spans="1:1">
       <c r="A326" s="19" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="327" spans="1:1" ht="13.9">
+    <row r="327" spans="1:1">
       <c r="A327" s="19" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="328" spans="1:1" ht="13.9">
+    <row r="328" spans="1:1">
       <c r="A328" s="19" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="329" spans="1:1" ht="13.9">
+    <row r="329" spans="1:1">
       <c r="A329" s="19" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="330" spans="1:1" ht="13.9">
+    <row r="330" spans="1:1">
       <c r="A330" s="19" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="331" spans="1:1" ht="13.9">
+    <row r="331" spans="1:1">
       <c r="A331" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:1" ht="13.9">
+    <row r="332" spans="1:1">
       <c r="A332" s="19" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="333" spans="1:1" ht="13.9">
+    <row r="333" spans="1:1">
       <c r="A333" s="19" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="334" spans="1:1" ht="13.9">
+    <row r="334" spans="1:1">
       <c r="A334" s="19" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="335" spans="1:1" ht="13.9">
+    <row r="335" spans="1:1">
       <c r="A335" s="19" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="336" spans="1:1" ht="13.9">
+    <row r="336" spans="1:1">
       <c r="A336" s="19" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="337" spans="1:1" ht="13.9">
+    <row r="337" spans="1:1">
       <c r="A337" s="19" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="338" spans="1:1" ht="13.9">
+    <row r="338" spans="1:1">
       <c r="A338" s="19" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="339" spans="1:1" ht="13.9">
+    <row r="339" spans="1:1">
       <c r="A339" s="19" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="340" spans="1:1" ht="13.9">
+    <row r="340" spans="1:1">
       <c r="A340" s="20" t="s">
         <v>337</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3677,12 +3646,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="52.875" customWidth="1"/>
+    <col min="2" max="2" width="52.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>338</v>
       </c>
@@ -3690,7 +3659,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="3" t="s">
         <v>340</v>
       </c>
@@ -3698,16 +3667,16 @@
         <v>43250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="67.5">
+    <row r="3" spans="1:2" ht="69">
       <c r="A3" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>343</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegist.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegist.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
   <si>
     <t>该投资者是否属于本行</t>
   </si>
@@ -1246,10 +1246,6 @@
   </si>
   <si>
     <t>34 SPV登记编码</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1460,7 +1456,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1516,11 +1512,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1528,6 +1519,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1813,95 +1811,115 @@
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21" style="21" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" style="21" customWidth="1"/>
-    <col min="3" max="5" width="21" style="21" customWidth="1"/>
-    <col min="6" max="6" width="27.21875" style="21" customWidth="1"/>
-    <col min="7" max="7" width="21" style="22" customWidth="1"/>
-    <col min="8" max="11" width="21" style="21" customWidth="1"/>
-    <col min="12" max="12" width="28.109375" style="21" customWidth="1"/>
-    <col min="13" max="14" width="21" style="21" customWidth="1"/>
-    <col min="15" max="15" width="31" style="21" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" style="21" customWidth="1"/>
-    <col min="17" max="23" width="21" style="21" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="23"/>
+    <col min="1" max="1" width="21" style="24" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="24" customWidth="1"/>
+    <col min="3" max="5" width="21" style="24" customWidth="1"/>
+    <col min="6" max="6" width="27.21875" style="24" customWidth="1"/>
+    <col min="7" max="7" width="21" style="25" customWidth="1"/>
+    <col min="8" max="11" width="21" style="24" customWidth="1"/>
+    <col min="12" max="12" width="28.109375" style="24" customWidth="1"/>
+    <col min="13" max="14" width="21" style="24" customWidth="1"/>
+    <col min="15" max="15" width="31" style="24" customWidth="1"/>
+    <col min="16" max="16" width="26.88671875" style="24" customWidth="1"/>
+    <col min="17" max="23" width="21" style="24" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="22" t="s">
         <v>351</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="22" t="s">
         <v>353</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="22" t="s">
         <v>355</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="P1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="24" t="s">
+      <c r="Q1" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="22" t="s">
         <v>357</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="S1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="24" t="s">
+      <c r="T1" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="U1" s="24" t="s">
+      <c r="U1" s="22" t="s">
         <v>359</v>
       </c>
-      <c r="V1" s="24" t="s">
+      <c r="V1" s="22" t="s">
         <v>360</v>
       </c>
-      <c r="W1" s="24" t="s">
+      <c r="W1" s="22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
-      <c r="A2" s="21" t="s">
-        <v>364</v>
-      </c>
+    <row r="2" spans="1:23" s="27" customFormat="1">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -3671,7 +3689,7 @@
       <c r="A3" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>343</v>
       </c>
     </row>
